--- a/Projecty-Managment.xlsx
+++ b/Projecty-Managment.xlsx
@@ -12,7 +12,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180"/>
   </bookViews>
   <sheets>
-    <sheet name="Chart" sheetId="1" r:id="rId1"/>
+    <sheet name="Gantt Chart" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -265,9 +265,10 @@
   <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color indexed="8"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -413,20 +414,8 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color indexed="63"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color indexed="49"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color indexed="19"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -447,6 +436,18 @@
     <font>
       <sz val="10"/>
       <color indexed="57"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color indexed="19"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color indexed="63"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -944,10 +945,10 @@
     <xf numFmtId="0" fontId="18" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -962,19 +963,19 @@
     <xf numFmtId="0" fontId="18" fillId="37" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="24" fillId="40" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="41" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="41" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1027,7 +1028,7 @@
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
@@ -1311,7 +1312,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N51"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
